--- a/test_samples/KUEHNE_NAGEL/sample1_ref.xlsx
+++ b/test_samples/KUEHNE_NAGEL/sample1_ref.xlsx
@@ -1,210 +1,64 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jeffrey.hu\Desktop\LC\供應商帳單\KUEHNE NAGEL_已OK\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D21D029A-3900-4EEA-8912-2F7D4B646159}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="819" xr2:uid="{B2E6A21A-966E-4572-9141-AA1879003F42}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="819" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="DWIHARTA" sheetId="3" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DWIHARTA" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="28">
-  <si>
-    <t>INVOICE DATE
-發票日期</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>INVOICE NO
-發票號碼</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SUPPLIER
-供應商名稱</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CONSIGNEE
-集團公司名稱</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Description
-費用名稱</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>AMOUNT
-金額</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Order No.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Arrive Date
-到達日</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>on board date
-開船日</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>B/L NO.
-提單號碼</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>MBL NO.
-主提單號碼</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Port of Loading
-啟運港</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Port of discharge
-目的港</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Volume
-材積</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Vessel
-船名</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Container no.
-貨櫃號碼</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>KUEHNE NAGEL INDONESIA</t>
-  </si>
-  <si>
-    <t>CAK1131228</t>
-  </si>
-  <si>
-    <t>PT. POU YUEN INDONESIA</t>
-  </si>
-  <si>
-    <t>23.08.2026</t>
-  </si>
-  <si>
-    <t>12.10.2026</t>
-  </si>
-  <si>
-    <t>N/A</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>JAKARTA</t>
-  </si>
-  <si>
-    <t>Los Angeles</t>
-  </si>
-  <si>
-    <t>CMA CGM WHITE SHARK</t>
-  </si>
-  <si>
-    <t>20.08.2026</t>
-  </si>
-  <si>
-    <t>OVERTIME CHARGES EXPORT</t>
-  </si>
-  <si>
-    <t>RYH0810074280</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="5">
     <font>
+      <name val="新細明體"/>
+      <charset val="136"/>
+      <family val="2"/>
+      <color theme="1"/>
       <sz val="12"/>
-      <color theme="1"/>
-      <name val="新細明體"/>
-      <family val="2"/>
-      <charset val="136"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="新細明體"/>
+      <charset val="136"/>
+      <family val="2"/>
       <sz val="9"/>
-      <name val="新細明體"/>
-      <family val="2"/>
-      <charset val="136"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="微軟正黑體"/>
+      <charset val="136"/>
+      <family val="2"/>
+      <color theme="1"/>
       <sz val="12"/>
-      <color theme="1"/>
-      <name val="微軟正黑體"/>
-      <family val="2"/>
-      <charset val="136"/>
     </font>
     <font>
+      <name val="微軟正黑體"/>
+      <charset val="136"/>
+      <family val="2"/>
+      <color theme="0"/>
       <sz val="12"/>
-      <color theme="0"/>
-      <name val="微軟正黑體"/>
-      <family val="2"/>
-      <charset val="136"/>
     </font>
     <font>
-      <b/>
+      <name val="新細明體"/>
+      <charset val="136"/>
+      <family val="1"/>
+      <b val="1"/>
+      <color theme="1"/>
       <sz val="12"/>
-      <color theme="1"/>
-      <name val="新細明體"/>
-      <family val="1"/>
-      <charset val="136"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -226,49 +80,109 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+  <cellXfs count="9">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="15" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="15" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -588,162 +502,241 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCF1381F-552A-4924-9A7A-4C0080F73CE6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:Q12"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
-    <col min="1" max="1" width="17.36328125" customWidth="1"/>
-    <col min="2" max="2" width="15.7265625" customWidth="1"/>
-    <col min="3" max="3" width="29.453125" customWidth="1"/>
-    <col min="4" max="4" width="26" customWidth="1"/>
-    <col min="5" max="5" width="25.453125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.90625" customWidth="1"/>
-    <col min="7" max="7" width="29.26953125" customWidth="1"/>
-    <col min="8" max="9" width="13.7265625" customWidth="1"/>
-    <col min="10" max="10" width="17.6328125" customWidth="1"/>
-    <col min="11" max="11" width="20" customWidth="1"/>
-    <col min="12" max="12" width="16.90625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="18.6328125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="16.36328125" customWidth="1"/>
-    <col min="15" max="15" width="7.6328125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="15.08984375" bestFit="1" customWidth="1"/>
+    <col width="17.36328125" customWidth="1" style="8" min="1" max="1"/>
+    <col width="15.7265625" customWidth="1" style="8" min="2" max="2"/>
+    <col width="29.453125" customWidth="1" style="8" min="3" max="3"/>
+    <col width="26" customWidth="1" style="8" min="4" max="4"/>
+    <col width="25.453125" bestFit="1" customWidth="1" style="8" min="5" max="5"/>
+    <col width="17.90625" customWidth="1" style="8" min="6" max="6"/>
+    <col width="29.26953125" customWidth="1" style="8" min="7" max="7"/>
+    <col width="13.7265625" customWidth="1" style="8" min="8" max="9"/>
+    <col width="17.6328125" customWidth="1" style="8" min="10" max="10"/>
+    <col width="20" customWidth="1" style="8" min="11" max="11"/>
+    <col width="16.90625" bestFit="1" customWidth="1" style="8" min="12" max="12"/>
+    <col width="18.6328125" bestFit="1" customWidth="1" style="8" min="13" max="13"/>
+    <col width="16.36328125" customWidth="1" style="8" min="14" max="14"/>
+    <col width="7.6328125" bestFit="1" customWidth="1" style="8" min="15" max="15"/>
+    <col width="15.08984375" bestFit="1" customWidth="1" style="8" min="16" max="16"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="1" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A2" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="B2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F2" s="4">
+    <row r="1" ht="45" customFormat="1" customHeight="1" s="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>INVOICE DATE
+發票日期</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>INVOICE NO
+發票號碼</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>SUPPLIER
+供應商名稱</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>CONSIGNEE
+集團公司名稱</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Description
+費用名稱</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>AMOUNT
+金額</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>Order No.</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>Arrive Date
+到達日</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>on board date
+開船日</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>B/L NO.
+提單號碼</t>
+        </is>
+      </c>
+      <c r="K1" s="2" t="inlineStr">
+        <is>
+          <t>MBL NO.
+主提單號碼</t>
+        </is>
+      </c>
+      <c r="L1" s="2" t="inlineStr">
+        <is>
+          <t>Port of Loading
+啟運港</t>
+        </is>
+      </c>
+      <c r="M1" s="2" t="inlineStr">
+        <is>
+          <t>Port of discharge
+目的港</t>
+        </is>
+      </c>
+      <c r="N1" s="2" t="inlineStr">
+        <is>
+          <t>Volume
+材積</t>
+        </is>
+      </c>
+      <c r="O1" s="2" t="inlineStr">
+        <is>
+          <t>Vessel
+船名</t>
+        </is>
+      </c>
+      <c r="P1" s="2" t="inlineStr">
+        <is>
+          <t>Container no.
+貨櫃號碼</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>20 Aug 2026</t>
+        </is>
+      </c>
+      <c r="B2" s="0" t="inlineStr">
+        <is>
+          <t>CAK1131228</t>
+        </is>
+      </c>
+      <c r="C2" s="0" t="inlineStr">
+        <is>
+          <t>KUEHNE NAGEL INDONESIA</t>
+        </is>
+      </c>
+      <c r="D2" s="0" t="inlineStr">
+        <is>
+          <t>PT. POU YUEN INDONESIA</t>
+        </is>
+      </c>
+      <c r="E2" s="0" t="inlineStr">
+        <is>
+          <t>OVERTIME CHARGES EXPORT</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="n">
         <v>1521098</v>
       </c>
-      <c r="G2" t="s">
-        <v>27</v>
-      </c>
-      <c r="H2" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="J2">
+      <c r="G2" s="0" t="inlineStr">
+        <is>
+          <t>RYH0810074280</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>12 Oct 2026</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>23 Aug 2026</t>
+        </is>
+      </c>
+      <c r="J2" s="0" t="n">
         <v>1076510528</v>
       </c>
-      <c r="K2" t="s">
-        <v>21</v>
-      </c>
-      <c r="L2" t="s">
-        <v>22</v>
-      </c>
-      <c r="M2" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="N2">
+      <c r="K2" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L2" s="0" t="inlineStr">
+        <is>
+          <t>JAKARTA</t>
+        </is>
+      </c>
+      <c r="M2" s="7" t="inlineStr">
+        <is>
+          <t>Los Angeles</t>
+        </is>
+      </c>
+      <c r="N2" s="0" t="n">
         <v>11.81</v>
       </c>
-      <c r="O2" t="s">
-        <v>24</v>
-      </c>
-      <c r="P2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A3" s="3"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A4" s="3"/>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A5" s="3"/>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A6" s="3"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A7" s="3"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A8" s="3"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="Q12" s="1"/>
+      <c r="O2" s="0" t="inlineStr">
+        <is>
+          <t>CMA CGM WHITE SHARK</t>
+        </is>
+      </c>
+      <c r="P2" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
+      <c r="I3" s="3" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
+      <c r="I4" s="3" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
+      <c r="I5" s="3" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
+      <c r="I6" s="3" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="n"/>
+      <c r="H7" s="3" t="n"/>
+      <c r="I7" s="3" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="n"/>
+      <c r="H8" s="3" t="n"/>
+      <c r="I8" s="3" t="n"/>
+    </row>
+    <row r="9"/>
+    <row r="10"/>
+    <row r="11"/>
+    <row r="12">
+      <c r="Q12" s="1" t="n"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/test_samples/KUEHNE_NAGEL/sample1_ref.xlsx
+++ b/test_samples/KUEHNE_NAGEL/sample1_ref.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="819" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="6510" yWindow="9375" windowWidth="28800" windowHeight="15315" tabRatio="819" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DWIHARTA" sheetId="1" state="visible" r:id="rId1"/>
@@ -507,24 +507,25 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
+  <dimension ref="A1:R12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
-    <col width="17.36328125" customWidth="1" style="8" min="1" max="1"/>
-    <col width="15.7265625" customWidth="1" style="8" min="2" max="2"/>
-    <col width="29.453125" customWidth="1" style="8" min="3" max="3"/>
+    <col width="17.375" customWidth="1" style="8" min="1" max="1"/>
+    <col width="15.75" customWidth="1" style="8" min="2" max="2"/>
+    <col width="29.5" customWidth="1" style="8" min="3" max="3"/>
     <col width="26" customWidth="1" style="8" min="4" max="4"/>
-    <col width="25.453125" bestFit="1" customWidth="1" style="8" min="5" max="5"/>
-    <col width="17.90625" customWidth="1" style="8" min="6" max="6"/>
-    <col width="29.26953125" customWidth="1" style="8" min="7" max="7"/>
-    <col width="13.7265625" customWidth="1" style="8" min="8" max="9"/>
-    <col width="17.6328125" customWidth="1" style="8" min="10" max="10"/>
-    <col width="20" customWidth="1" style="8" min="11" max="11"/>
-    <col width="16.90625" bestFit="1" customWidth="1" style="8" min="12" max="12"/>
-    <col width="18.6328125" bestFit="1" customWidth="1" style="8" min="13" max="13"/>
-    <col width="16.36328125" customWidth="1" style="8" min="14" max="14"/>
-    <col width="7.6328125" bestFit="1" customWidth="1" style="8" min="15" max="15"/>
-    <col width="15.08984375" bestFit="1" customWidth="1" style="8" min="16" max="16"/>
+    <col width="25.5" bestFit="1" customWidth="1" style="8" min="5" max="5"/>
+    <col width="17.875" customWidth="1" style="8" min="6" max="7"/>
+    <col width="29.25" customWidth="1" style="8" min="8" max="8"/>
+    <col width="13.75" customWidth="1" style="8" min="9" max="10"/>
+    <col width="17.625" customWidth="1" style="8" min="11" max="11"/>
+    <col width="20" customWidth="1" style="8" min="12" max="12"/>
+    <col width="16.875" bestFit="1" customWidth="1" style="8" min="13" max="13"/>
+    <col width="18.625" bestFit="1" customWidth="1" style="8" min="14" max="14"/>
+    <col width="16.375" customWidth="1" style="8" min="15" max="15"/>
+    <col width="7.625" bestFit="1" customWidth="1" style="8" min="16" max="16"/>
+    <col width="15.125" bestFit="1" customWidth="1" style="8" min="17" max="17"/>
+    <col width="13.375" customWidth="1" style="8" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1" ht="45" customFormat="1" customHeight="1" s="1">
@@ -566,63 +567,74 @@
       </c>
       <c r="G1" s="2" t="inlineStr">
         <is>
+          <t>VAT</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
           <t>Order No.</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>Arrive Date
 到達日</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>on board date
 開船日</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="K1" s="2" t="inlineStr">
         <is>
           <t>B/L NO.
 提單號碼</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="L1" s="2" t="inlineStr">
         <is>
           <t>MBL NO.
 主提單號碼</t>
         </is>
       </c>
-      <c r="L1" s="2" t="inlineStr">
+      <c r="M1" s="2" t="inlineStr">
         <is>
           <t>Port of Loading
 啟運港</t>
         </is>
       </c>
-      <c r="M1" s="2" t="inlineStr">
+      <c r="N1" s="2" t="inlineStr">
         <is>
           <t>Port of discharge
 目的港</t>
         </is>
       </c>
-      <c r="N1" s="2" t="inlineStr">
+      <c r="O1" s="2" t="inlineStr">
         <is>
           <t>Volume
 材積</t>
         </is>
       </c>
-      <c r="O1" s="2" t="inlineStr">
+      <c r="P1" s="2" t="inlineStr">
         <is>
           <t>Vessel
 船名</t>
         </is>
       </c>
-      <c r="P1" s="2" t="inlineStr">
+      <c r="Q1" s="2" t="inlineStr">
         <is>
           <t>Container no.
 貨櫃號碼</t>
         </is>
       </c>
+      <c r="R1" s="2" t="inlineStr">
+        <is>
+          <t>Shipper
+出貨方</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
@@ -653,88 +665,96 @@
       <c r="F2" s="4" t="n">
         <v>1521098</v>
       </c>
-      <c r="G2" s="0" t="inlineStr">
+      <c r="G2" s="4" t="n">
+        <v>167321</v>
+      </c>
+      <c r="H2" s="0" t="inlineStr">
         <is>
           <t>RYH0810074280</t>
         </is>
       </c>
-      <c r="H2" s="5" t="inlineStr">
+      <c r="I2" s="5" t="inlineStr">
         <is>
           <t>12 Oct 2026</t>
         </is>
       </c>
-      <c r="I2" s="3" t="inlineStr">
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>23 Aug 2026</t>
         </is>
       </c>
-      <c r="J2" s="0" t="n">
+      <c r="K2" s="0" t="n">
         <v>1076510528</v>
       </c>
-      <c r="K2" s="0" t="inlineStr">
+      <c r="L2" s="0" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="L2" s="0" t="inlineStr">
+      <c r="M2" s="0" t="inlineStr">
         <is>
           <t>JAKARTA</t>
         </is>
       </c>
-      <c r="M2" s="7" t="inlineStr">
+      <c r="N2" s="7" t="inlineStr">
         <is>
           <t>Los Angeles</t>
         </is>
       </c>
-      <c r="N2" s="0" t="n">
+      <c r="O2" s="0" t="n">
         <v>11.81</v>
       </c>
-      <c r="O2" s="0" t="inlineStr">
+      <c r="P2" s="0" t="inlineStr">
         <is>
           <t>CMA CGM WHITE SHARK</t>
         </is>
       </c>
-      <c r="P2" s="0" t="inlineStr">
+      <c r="Q2" s="0" t="inlineStr">
         <is>
           <t>N/A</t>
+        </is>
+      </c>
+      <c r="R2" s="0" t="inlineStr">
+        <is>
+          <t>PT. POU YUEN INDONESIA</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="n"/>
-      <c r="H3" s="3" t="n"/>
       <c r="I3" s="3" t="n"/>
+      <c r="J3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="n"/>
-      <c r="H4" s="3" t="n"/>
       <c r="I4" s="3" t="n"/>
+      <c r="J4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n"/>
-      <c r="H5" s="3" t="n"/>
       <c r="I5" s="3" t="n"/>
+      <c r="J5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="n"/>
-      <c r="H6" s="3" t="n"/>
       <c r="I6" s="3" t="n"/>
+      <c r="J6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n"/>
-      <c r="H7" s="3" t="n"/>
       <c r="I7" s="3" t="n"/>
+      <c r="J7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="n"/>
-      <c r="H8" s="3" t="n"/>
       <c r="I8" s="3" t="n"/>
+      <c r="J8" s="3" t="n"/>
     </row>
     <row r="9"/>
     <row r="10"/>
     <row r="11"/>
     <row r="12">
-      <c r="Q12" s="1" t="n"/>
+      <c r="R12" s="1" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/test_samples/KUEHNE_NAGEL/sample1_ref.xlsx
+++ b/test_samples/KUEHNE_NAGEL/sample1_ref.xlsx
@@ -1,64 +1,208 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <workbookPr defaultThemeVersion="202300"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jeffrey.hu\Desktop\印尼供應商帳單\KUEHNE NAGEL________________OK  VAT已改\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6933ED87-0170-4451-94EF-53278D7224FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="6510" yWindow="9375" windowWidth="28800" windowHeight="15315" tabRatio="819" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="6855" yWindow="2535" windowWidth="28800" windowHeight="15510" tabRatio="819" xr2:uid="{B2E6A21A-966E-4572-9141-AA1879003F42}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DWIHARTA" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="DWIHARTA" sheetId="3" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="27">
+  <si>
+    <t>INVOICE DATE
+發票日期</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>INVOICE NO
+發票號碼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SUPPLIER
+供應商名稱</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CONSIGNEE
+集團公司名稱</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Description
+費用名稱</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AMOUNT
+金額</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Order No.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Arrive Date
+到達日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>on board date
+開船日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>B/L NO.
+提單號碼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MBL NO.
+主提單號碼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Port of Loading
+啟運港</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Port of discharge
+目的港</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Volume
+材積</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Vessel
+船名</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Container no.
+貨櫃號碼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KUEHNE NAGEL INDONESIA</t>
+  </si>
+  <si>
+    <t>CAK1131228</t>
+  </si>
+  <si>
+    <t>PT. POU YUEN INDONESIA</t>
+  </si>
+  <si>
+    <t>N/A</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>JAKARTA</t>
+  </si>
+  <si>
+    <t>Los Angeles</t>
+  </si>
+  <si>
+    <t>CMA CGM WHITE SHARK</t>
+  </si>
+  <si>
+    <t>OVERTIME CHARGES EXPORT</t>
+  </si>
+  <si>
+    <t>RYH0810074280</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>VAT</t>
+  </si>
+  <si>
+    <t>Shipper
+出貨方</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="5">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
+      <sz val="12"/>
+      <color theme="1"/>
       <name val="新細明體"/>
+      <family val="2"/>
       <charset val="136"/>
-      <family val="2"/>
-      <color theme="1"/>
-      <sz val="12"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9"/>
       <name val="新細明體"/>
+      <family val="2"/>
       <charset val="136"/>
-      <family val="2"/>
-      <sz val="9"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="12"/>
+      <color theme="1"/>
       <name val="微軟正黑體"/>
+      <family val="2"/>
       <charset val="136"/>
-      <family val="2"/>
-      <color theme="1"/>
-      <sz val="12"/>
     </font>
     <font>
+      <sz val="12"/>
+      <color theme="0"/>
       <name val="微軟正黑體"/>
+      <family val="2"/>
       <charset val="136"/>
-      <family val="2"/>
-      <color theme="0"/>
-      <sz val="12"/>
     </font>
     <font>
+      <sz val="12"/>
+      <color theme="1"/>
       <name val="新細明體"/>
+      <family val="1"/>
       <charset val="136"/>
-      <family val="1"/>
-      <b val="1"/>
-      <color theme="1"/>
-      <sz val="12"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -80,109 +224,46 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="7">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="15" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -502,261 +583,220 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCF1381F-552A-4924-9A7A-4C0080F73CE6}">
   <dimension ref="A1:R12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col width="17.375" customWidth="1" style="8" min="1" max="1"/>
-    <col width="15.75" customWidth="1" style="8" min="2" max="2"/>
-    <col width="29.5" customWidth="1" style="8" min="3" max="3"/>
-    <col width="26" customWidth="1" style="8" min="4" max="4"/>
-    <col width="25.5" bestFit="1" customWidth="1" style="8" min="5" max="5"/>
-    <col width="17.875" customWidth="1" style="8" min="6" max="7"/>
-    <col width="29.25" customWidth="1" style="8" min="8" max="8"/>
-    <col width="13.75" customWidth="1" style="8" min="9" max="10"/>
-    <col width="17.625" customWidth="1" style="8" min="11" max="11"/>
-    <col width="20" customWidth="1" style="8" min="12" max="12"/>
-    <col width="16.875" bestFit="1" customWidth="1" style="8" min="13" max="13"/>
-    <col width="18.625" bestFit="1" customWidth="1" style="8" min="14" max="14"/>
-    <col width="16.375" customWidth="1" style="8" min="15" max="15"/>
-    <col width="7.625" bestFit="1" customWidth="1" style="8" min="16" max="16"/>
-    <col width="15.125" bestFit="1" customWidth="1" style="8" min="17" max="17"/>
-    <col width="13.375" customWidth="1" style="8" min="18" max="18"/>
+    <col min="1" max="1" width="17.375" customWidth="1"/>
+    <col min="2" max="2" width="15.75" customWidth="1"/>
+    <col min="3" max="3" width="29.5" customWidth="1"/>
+    <col min="4" max="4" width="26" customWidth="1"/>
+    <col min="5" max="5" width="25.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="17.875" customWidth="1"/>
+    <col min="8" max="8" width="29.25" customWidth="1"/>
+    <col min="9" max="10" width="13.75" customWidth="1"/>
+    <col min="11" max="11" width="17.625" customWidth="1"/>
+    <col min="12" max="12" width="20" customWidth="1"/>
+    <col min="13" max="13" width="16.875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="18.625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="16.375" customWidth="1"/>
+    <col min="16" max="16" width="7.625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="15.125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="45" customFormat="1" customHeight="1" s="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>INVOICE DATE
-發票日期</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>INVOICE NO
-發票號碼</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>SUPPLIER
-供應商名稱</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>CONSIGNEE
-集團公司名稱</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>Description
-費用名稱</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
-        <is>
-          <t>AMOUNT
-金額</t>
-        </is>
-      </c>
-      <c r="G1" s="2" t="inlineStr">
-        <is>
-          <t>VAT</t>
-        </is>
-      </c>
-      <c r="H1" s="2" t="inlineStr">
-        <is>
-          <t>Order No.</t>
-        </is>
-      </c>
-      <c r="I1" s="2" t="inlineStr">
-        <is>
-          <t>Arrive Date
-到達日</t>
-        </is>
-      </c>
-      <c r="J1" s="2" t="inlineStr">
-        <is>
-          <t>on board date
-開船日</t>
-        </is>
-      </c>
-      <c r="K1" s="2" t="inlineStr">
-        <is>
-          <t>B/L NO.
-提單號碼</t>
-        </is>
-      </c>
-      <c r="L1" s="2" t="inlineStr">
-        <is>
-          <t>MBL NO.
-主提單號碼</t>
-        </is>
-      </c>
-      <c r="M1" s="2" t="inlineStr">
-        <is>
-          <t>Port of Loading
-啟運港</t>
-        </is>
-      </c>
-      <c r="N1" s="2" t="inlineStr">
-        <is>
-          <t>Port of discharge
-目的港</t>
-        </is>
-      </c>
-      <c r="O1" s="2" t="inlineStr">
-        <is>
-          <t>Volume
-材積</t>
-        </is>
-      </c>
-      <c r="P1" s="2" t="inlineStr">
-        <is>
-          <t>Vessel
-船名</t>
-        </is>
-      </c>
-      <c r="Q1" s="2" t="inlineStr">
-        <is>
-          <t>Container no.
-貨櫃號碼</t>
-        </is>
-      </c>
-      <c r="R1" s="2" t="inlineStr">
-        <is>
-          <t>Shipper
-出貨方</t>
-        </is>
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="R1" s="2" t="s">
+        <v>26</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>20 Aug 2026</t>
-        </is>
-      </c>
-      <c r="B2" s="0" t="inlineStr">
-        <is>
-          <t>CAK1131228</t>
-        </is>
-      </c>
-      <c r="C2" s="0" t="inlineStr">
-        <is>
-          <t>KUEHNE NAGEL INDONESIA</t>
-        </is>
-      </c>
-      <c r="D2" s="0" t="inlineStr">
-        <is>
-          <t>PT. POU YUEN INDONESIA</t>
-        </is>
-      </c>
-      <c r="E2" s="0" t="inlineStr">
-        <is>
-          <t>OVERTIME CHARGES EXPORT</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="n">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A2" s="5">
+        <v>46254</v>
+      </c>
+      <c r="B2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F2" s="4">
         <v>1521098</v>
       </c>
-      <c r="G2" s="4" t="n">
+      <c r="H2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I2" s="5">
+        <v>46307</v>
+      </c>
+      <c r="J2" s="5">
+        <v>46257</v>
+      </c>
+      <c r="K2">
+        <v>1076510528</v>
+      </c>
+      <c r="L2" t="s">
+        <v>19</v>
+      </c>
+      <c r="M2" t="s">
+        <v>20</v>
+      </c>
+      <c r="N2" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="O2">
+        <v>11.81</v>
+      </c>
+      <c r="P2" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>19</v>
+      </c>
+      <c r="R2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A3" s="5">
+        <v>46254</v>
+      </c>
+      <c r="B3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3" s="4">
         <v>167321</v>
       </c>
-      <c r="H2" s="0" t="inlineStr">
-        <is>
-          <t>RYH0810074280</t>
-        </is>
-      </c>
-      <c r="I2" s="5" t="inlineStr">
-        <is>
-          <t>12 Oct 2026</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>23 Aug 2026</t>
-        </is>
-      </c>
-      <c r="K2" s="0" t="n">
+      <c r="H3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I3" s="5">
+        <v>46307</v>
+      </c>
+      <c r="J3" s="5">
+        <v>46257</v>
+      </c>
+      <c r="K3">
         <v>1076510528</v>
       </c>
-      <c r="L2" s="0" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M2" s="0" t="inlineStr">
-        <is>
-          <t>JAKARTA</t>
-        </is>
-      </c>
-      <c r="N2" s="7" t="inlineStr">
-        <is>
-          <t>Los Angeles</t>
-        </is>
-      </c>
-      <c r="O2" s="0" t="n">
+      <c r="L3" t="s">
+        <v>19</v>
+      </c>
+      <c r="M3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N3" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="O3">
         <v>11.81</v>
       </c>
-      <c r="P2" s="0" t="inlineStr">
-        <is>
-          <t>CMA CGM WHITE SHARK</t>
-        </is>
-      </c>
-      <c r="Q2" s="0" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R2" s="0" t="inlineStr">
-        <is>
-          <t>PT. POU YUEN INDONESIA</t>
-        </is>
+      <c r="P3" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>19</v>
+      </c>
+      <c r="R3" t="s">
+        <v>18</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="3" t="n"/>
-      <c r="I3" s="3" t="n"/>
-      <c r="J3" s="3" t="n"/>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A4" s="3"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3"/>
+      <c r="N4" s="6"/>
     </row>
-    <row r="4">
-      <c r="A4" s="3" t="n"/>
-      <c r="I4" s="3" t="n"/>
-      <c r="J4" s="3" t="n"/>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A5" s="3"/>
+      <c r="I5" s="3"/>
+      <c r="J5" s="3"/>
+      <c r="N5" s="6"/>
     </row>
-    <row r="5">
-      <c r="A5" s="3" t="n"/>
-      <c r="I5" s="3" t="n"/>
-      <c r="J5" s="3" t="n"/>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A6" s="3"/>
+      <c r="I6" s="3"/>
+      <c r="J6" s="3"/>
+      <c r="N6" s="6"/>
     </row>
-    <row r="6">
-      <c r="A6" s="3" t="n"/>
-      <c r="I6" s="3" t="n"/>
-      <c r="J6" s="3" t="n"/>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A7" s="3"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="3"/>
     </row>
-    <row r="7">
-      <c r="A7" s="3" t="n"/>
-      <c r="I7" s="3" t="n"/>
-      <c r="J7" s="3" t="n"/>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A8" s="3"/>
+      <c r="I8" s="3"/>
+      <c r="J8" s="3"/>
     </row>
-    <row r="8">
-      <c r="A8" s="3" t="n"/>
-      <c r="I8" s="3" t="n"/>
-      <c r="J8" s="3" t="n"/>
-    </row>
-    <row r="9"/>
-    <row r="10"/>
-    <row r="11"/>
-    <row r="12">
-      <c r="R12" s="1" t="n"/>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="R12" s="1"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/test_samples/KUEHNE_NAGEL/sample1_ref.xlsx
+++ b/test_samples/KUEHNE_NAGEL/sample1_ref.xlsx
@@ -1,208 +1,63 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jeffrey.hu\Desktop\印尼供應商帳單\KUEHNE NAGEL________________OK  VAT已改\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6933ED87-0170-4451-94EF-53278D7224FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="6855" yWindow="2535" windowWidth="28800" windowHeight="15510" tabRatio="819" xr2:uid="{B2E6A21A-966E-4572-9141-AA1879003F42}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="6855" yWindow="2535" windowWidth="28800" windowHeight="15510" tabRatio="819" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="DWIHARTA" sheetId="3" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DWIHARTA" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="27">
-  <si>
-    <t>INVOICE DATE
-發票日期</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>INVOICE NO
-發票號碼</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SUPPLIER
-供應商名稱</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CONSIGNEE
-集團公司名稱</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Description
-費用名稱</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>AMOUNT
-金額</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Order No.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Arrive Date
-到達日</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>on board date
-開船日</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>B/L NO.
-提單號碼</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>MBL NO.
-主提單號碼</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Port of Loading
-啟運港</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Port of discharge
-目的港</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Volume
-材積</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Vessel
-船名</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Container no.
-貨櫃號碼</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>KUEHNE NAGEL INDONESIA</t>
-  </si>
-  <si>
-    <t>CAK1131228</t>
-  </si>
-  <si>
-    <t>PT. POU YUEN INDONESIA</t>
-  </si>
-  <si>
-    <t>N/A</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>JAKARTA</t>
-  </si>
-  <si>
-    <t>Los Angeles</t>
-  </si>
-  <si>
-    <t>CMA CGM WHITE SHARK</t>
-  </si>
-  <si>
-    <t>OVERTIME CHARGES EXPORT</t>
-  </si>
-  <si>
-    <t>RYH0810074280</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>VAT</t>
-  </si>
-  <si>
-    <t>Shipper
-出貨方</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="5">
     <font>
+      <name val="新細明體"/>
+      <charset val="136"/>
+      <family val="2"/>
+      <color theme="1"/>
       <sz val="12"/>
-      <color theme="1"/>
-      <name val="新細明體"/>
-      <family val="2"/>
-      <charset val="136"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="新細明體"/>
+      <charset val="136"/>
+      <family val="2"/>
       <sz val="9"/>
-      <name val="新細明體"/>
-      <family val="2"/>
-      <charset val="136"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="微軟正黑體"/>
+      <charset val="136"/>
+      <family val="2"/>
+      <color theme="1"/>
       <sz val="12"/>
-      <color theme="1"/>
-      <name val="微軟正黑體"/>
-      <family val="2"/>
-      <charset val="136"/>
     </font>
     <font>
+      <name val="微軟正黑體"/>
+      <charset val="136"/>
+      <family val="2"/>
+      <color theme="0"/>
       <sz val="12"/>
-      <color theme="0"/>
-      <name val="微軟正黑體"/>
-      <family val="2"/>
-      <charset val="136"/>
     </font>
     <font>
+      <name val="新細明體"/>
+      <charset val="136"/>
+      <family val="1"/>
+      <color theme="1"/>
       <sz val="12"/>
-      <color theme="1"/>
-      <name val="新細明體"/>
-      <family val="1"/>
-      <charset val="136"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -224,46 +79,106 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+  <cellXfs count="8">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -583,220 +498,320 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCF1381F-552A-4924-9A7A-4C0080F73CE6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:R12"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="17.375" customWidth="1"/>
-    <col min="2" max="2" width="15.75" customWidth="1"/>
-    <col min="3" max="3" width="29.5" customWidth="1"/>
-    <col min="4" max="4" width="26" customWidth="1"/>
-    <col min="5" max="5" width="25.5" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="17.875" customWidth="1"/>
-    <col min="8" max="8" width="29.25" customWidth="1"/>
-    <col min="9" max="10" width="13.75" customWidth="1"/>
-    <col min="11" max="11" width="17.625" customWidth="1"/>
-    <col min="12" max="12" width="20" customWidth="1"/>
-    <col min="13" max="13" width="16.875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="18.625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="16.375" customWidth="1"/>
-    <col min="16" max="16" width="7.625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="15.125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.375" customWidth="1"/>
+    <col width="17.375" customWidth="1" style="7" min="1" max="1"/>
+    <col width="15.75" customWidth="1" style="7" min="2" max="2"/>
+    <col width="29.5" customWidth="1" style="7" min="3" max="3"/>
+    <col width="26" customWidth="1" style="7" min="4" max="4"/>
+    <col width="25.5" bestFit="1" customWidth="1" style="7" min="5" max="5"/>
+    <col width="17.875" customWidth="1" style="7" min="6" max="7"/>
+    <col width="29.25" customWidth="1" style="7" min="8" max="8"/>
+    <col width="13.75" customWidth="1" style="7" min="9" max="10"/>
+    <col width="17.625" customWidth="1" style="7" min="11" max="11"/>
+    <col width="20" customWidth="1" style="7" min="12" max="12"/>
+    <col width="16.875" bestFit="1" customWidth="1" style="7" min="13" max="13"/>
+    <col width="18.625" bestFit="1" customWidth="1" style="7" min="14" max="14"/>
+    <col width="16.375" customWidth="1" style="7" min="15" max="15"/>
+    <col width="7.625" bestFit="1" customWidth="1" style="7" min="16" max="16"/>
+    <col width="15.125" bestFit="1" customWidth="1" style="7" min="17" max="17"/>
+    <col width="13.375" customWidth="1" style="7" min="18" max="18"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="O1" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="P1" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q1" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="R1" s="2" t="s">
-        <v>26</v>
+    <row r="1" ht="45" customFormat="1" customHeight="1" s="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>INVOICE DATE
+發票日期</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>INVOICE NO
+發票號碼</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>SUPPLIER
+供應商名稱</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>CONSIGNEE
+集團公司名稱</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Description
+費用名稱</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>AMOUNT
+金額</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>VAT</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>Order No.</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>Arrive Date
+到達日</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>on board date
+開船日</t>
+        </is>
+      </c>
+      <c r="K1" s="2" t="inlineStr">
+        <is>
+          <t>B/L NO.
+提單號碼</t>
+        </is>
+      </c>
+      <c r="L1" s="2" t="inlineStr">
+        <is>
+          <t>MBL NO.
+主提單號碼</t>
+        </is>
+      </c>
+      <c r="M1" s="2" t="inlineStr">
+        <is>
+          <t>Port of Loading
+啟運港</t>
+        </is>
+      </c>
+      <c r="N1" s="2" t="inlineStr">
+        <is>
+          <t>Port of discharge
+目的港</t>
+        </is>
+      </c>
+      <c r="O1" s="2" t="inlineStr">
+        <is>
+          <t>Volume
+材積</t>
+        </is>
+      </c>
+      <c r="P1" s="2" t="inlineStr">
+        <is>
+          <t>Vessel
+船名</t>
+        </is>
+      </c>
+      <c r="Q1" s="2" t="inlineStr">
+        <is>
+          <t>Container no.
+貨櫃號碼</t>
+        </is>
+      </c>
+      <c r="R1" s="2" t="inlineStr">
+        <is>
+          <t>Shipper
+出貨方</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A2" s="5">
+    <row r="2">
+      <c r="A2" s="5" t="n">
         <v>46254</v>
       </c>
-      <c r="B2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F2" s="4">
+      <c r="B2" s="0" t="inlineStr">
+        <is>
+          <t>CAK1131228</t>
+        </is>
+      </c>
+      <c r="C2" s="0" t="inlineStr">
+        <is>
+          <t>KUEHNE NAGEL INDONESIA</t>
+        </is>
+      </c>
+      <c r="D2" s="0" t="inlineStr">
+        <is>
+          <t>PT. POU YUEN INDONESIA</t>
+        </is>
+      </c>
+      <c r="E2" s="0" t="inlineStr">
+        <is>
+          <t>OVERTIME CHARGES EXPORT</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="n">
         <v>1521098</v>
       </c>
-      <c r="H2" t="s">
-        <v>24</v>
-      </c>
-      <c r="I2" s="5">
+      <c r="H2" s="0" t="inlineStr">
+        <is>
+          <t>RYH0810074280</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="n">
         <v>46307</v>
       </c>
-      <c r="J2" s="5">
+      <c r="J2" s="5" t="n">
         <v>46257</v>
       </c>
-      <c r="K2">
+      <c r="K2" s="0" t="n">
         <v>1076510528</v>
       </c>
-      <c r="L2" t="s">
-        <v>19</v>
-      </c>
-      <c r="M2" t="s">
-        <v>20</v>
-      </c>
-      <c r="N2" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="O2">
+      <c r="L2" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M2" s="0" t="inlineStr">
+        <is>
+          <t>JAKARTA</t>
+        </is>
+      </c>
+      <c r="N2" s="6" t="inlineStr">
+        <is>
+          <t>Los Angeles</t>
+        </is>
+      </c>
+      <c r="O2" s="0" t="n">
         <v>11.81</v>
       </c>
-      <c r="P2" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>19</v>
-      </c>
-      <c r="R2" t="s">
-        <v>18</v>
+      <c r="P2" s="0" t="inlineStr">
+        <is>
+          <t>CMA CGM WHITE SHARK 0GVNQE1MA</t>
+        </is>
+      </c>
+      <c r="Q2" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R2" s="0" t="inlineStr">
+        <is>
+          <t>PT. POU YUEN INDONESIA</t>
+        </is>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A3" s="5">
+    <row r="3">
+      <c r="A3" s="5" t="n">
         <v>46254</v>
       </c>
-      <c r="B3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" t="s">
-        <v>18</v>
-      </c>
-      <c r="G3" s="4">
+      <c r="B3" s="0" t="inlineStr">
+        <is>
+          <t>CAK1131228</t>
+        </is>
+      </c>
+      <c r="C3" s="0" t="inlineStr">
+        <is>
+          <t>KUEHNE NAGEL INDONESIA</t>
+        </is>
+      </c>
+      <c r="D3" s="0" t="inlineStr">
+        <is>
+          <t>PT. POU YUEN INDONESIA</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="n">
         <v>167321</v>
       </c>
-      <c r="H3" t="s">
-        <v>24</v>
-      </c>
-      <c r="I3" s="5">
+      <c r="H3" s="0" t="inlineStr">
+        <is>
+          <t>RYH0810074280</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="n">
         <v>46307</v>
       </c>
-      <c r="J3" s="5">
+      <c r="J3" s="5" t="n">
         <v>46257</v>
       </c>
-      <c r="K3">
+      <c r="K3" s="0" t="n">
         <v>1076510528</v>
       </c>
-      <c r="L3" t="s">
-        <v>19</v>
-      </c>
-      <c r="M3" t="s">
-        <v>20</v>
-      </c>
-      <c r="N3" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="O3">
+      <c r="L3" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M3" s="0" t="inlineStr">
+        <is>
+          <t>JAKARTA</t>
+        </is>
+      </c>
+      <c r="N3" s="6" t="inlineStr">
+        <is>
+          <t>Los Angeles</t>
+        </is>
+      </c>
+      <c r="O3" s="0" t="n">
         <v>11.81</v>
       </c>
-      <c r="P3" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>19</v>
-      </c>
-      <c r="R3" t="s">
-        <v>18</v>
+      <c r="P3" s="0" t="inlineStr">
+        <is>
+          <t>CMA CGM WHITE SHARK 0GVNQE1MA</t>
+        </is>
+      </c>
+      <c r="Q3" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R3" s="0" t="inlineStr">
+        <is>
+          <t>PT. POU YUEN INDONESIA</t>
+        </is>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A4" s="3"/>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
-      <c r="N4" s="6"/>
+    <row r="4">
+      <c r="A4" s="3" t="n"/>
+      <c r="I4" s="3" t="n"/>
+      <c r="J4" s="3" t="n"/>
+      <c r="N4" s="6" t="n"/>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A5" s="3"/>
-      <c r="I5" s="3"/>
-      <c r="J5" s="3"/>
-      <c r="N5" s="6"/>
+    <row r="5">
+      <c r="A5" s="3" t="n"/>
+      <c r="I5" s="3" t="n"/>
+      <c r="J5" s="3" t="n"/>
+      <c r="N5" s="6" t="n"/>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A6" s="3"/>
-      <c r="I6" s="3"/>
-      <c r="J6" s="3"/>
-      <c r="N6" s="6"/>
+    <row r="6">
+      <c r="A6" s="3" t="n"/>
+      <c r="I6" s="3" t="n"/>
+      <c r="J6" s="3" t="n"/>
+      <c r="N6" s="6" t="n"/>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A7" s="3"/>
-      <c r="I7" s="3"/>
-      <c r="J7" s="3"/>
+    <row r="7">
+      <c r="A7" s="3" t="n"/>
+      <c r="I7" s="3" t="n"/>
+      <c r="J7" s="3" t="n"/>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A8" s="3"/>
-      <c r="I8" s="3"/>
-      <c r="J8" s="3"/>
+    <row r="8">
+      <c r="A8" s="3" t="n"/>
+      <c r="I8" s="3" t="n"/>
+      <c r="J8" s="3" t="n"/>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="R12" s="1"/>
+    <row r="9"/>
+    <row r="10"/>
+    <row r="11"/>
+    <row r="12">
+      <c r="R12" s="1" t="n"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/test_samples/KUEHNE_NAGEL/sample1_ref.xlsx
+++ b/test_samples/KUEHNE_NAGEL/sample1_ref.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="6855" yWindow="2535" windowWidth="28800" windowHeight="15510" tabRatio="819" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DWIHARTA" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="DWIHARTA" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -726,6 +726,11 @@
           <t>PT. POU YUEN INDONESIA</t>
         </is>
       </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>VAT</t>
+        </is>
+      </c>
       <c r="G3" s="4" t="n">
         <v>167321</v>
       </c>
